--- a/templates/forms/care_service_meeting_notice.xlsx
+++ b/templates/forms/care_service_meeting_notice.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CareManagementTool\templates\forms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E9B6C8A-F7A0-4AA5-9A45-B1017EA1BEA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED92970D-4FF7-48C7-8ED4-9A60BB33636F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="10635" windowHeight="10725" xr2:uid="{4F7A4A16-936C-4EFE-B617-BAF543D176B9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4F7A4A16-936C-4EFE-B617-BAF543D176B9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,37 +25,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
-  <si>
-    <t>ローレル薬局</t>
-    <phoneticPr fontId="4"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>様</t>
     <rPh sb="0" eb="1">
       <t>サマ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>居宅介護支援事業所　安濃津ろまん</t>
-    <rPh sb="0" eb="1">
-      <t>キョ</t>
-    </rPh>
-    <rPh sb="1" eb="2">
-      <t>タク</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>カイゴ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>シエン</t>
-    </rPh>
-    <rPh sb="6" eb="9">
-      <t>ジギョウショ</t>
-    </rPh>
-    <rPh sb="10" eb="16">
-      <t>ア</t>
     </rPh>
     <phoneticPr fontId="4"/>
   </si>
@@ -175,13 +149,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>月</t>
-    <rPh sb="0" eb="1">
-      <t>ゲツ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>曜日 )</t>
     <rPh sb="0" eb="2">
       <t>ヨウビ</t>
@@ -196,10 +163,6 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>13：30</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>開催予定場所</t>
     <rPh sb="0" eb="2">
       <t>カイサイ</t>
@@ -209,16 +172,6 @@
     </rPh>
     <rPh sb="4" eb="6">
       <t>バショ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>安濃津ろまん　相談室</t>
-    <rPh sb="0" eb="6">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="7" eb="10">
-      <t>ソウダンシツ</t>
     </rPh>
     <phoneticPr fontId="4"/>
   </si>
@@ -252,28 +205,6 @@
     </rPh>
     <rPh sb="5" eb="7">
       <t>ナイヨウ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>安濃津ろまん入居に伴い、介護サービスについて検討する</t>
-    <rPh sb="0" eb="2">
-      <t>アノウ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ツ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ニュウキョ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>トモナ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>カイゴ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>ケントウ</t>
     </rPh>
     <phoneticPr fontId="4"/>
   </si>
@@ -619,12 +550,45 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -637,21 +601,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -668,27 +620,6 @@
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
@@ -1055,21 +986,19 @@
       <c r="AK1" s="2"/>
     </row>
     <row r="2" spans="1:54" s="19" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="21"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="22" t="s">
         <v>0</v>
-      </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="22" t="s">
-        <v>1</v>
       </c>
       <c r="M2" s="22"/>
       <c r="N2" s="2"/>
@@ -1087,31 +1016,28 @@
       <c r="Z2" s="3"/>
       <c r="AA2" s="3"/>
       <c r="AB2" s="3"/>
-      <c r="AC2" s="44">
-        <f ca="1">TODAY()</f>
-        <v>45985</v>
-      </c>
-      <c r="AD2" s="44"/>
-      <c r="AE2" s="44"/>
-      <c r="AF2" s="44"/>
-      <c r="AG2" s="44"/>
-      <c r="AH2" s="44"/>
-      <c r="AI2" s="44"/>
-      <c r="AJ2" s="44"/>
-      <c r="AK2" s="44"/>
+      <c r="AC2" s="23"/>
+      <c r="AD2" s="23"/>
+      <c r="AE2" s="23"/>
+      <c r="AF2" s="23"/>
+      <c r="AG2" s="23"/>
+      <c r="AH2" s="23"/>
+      <c r="AI2" s="23"/>
+      <c r="AJ2" s="23"/>
+      <c r="AK2" s="23"/>
     </row>
     <row r="3" spans="1:54" s="19" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="27"/>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
-      <c r="J3" s="27"/>
-      <c r="K3" s="27"/>
+      <c r="A3" s="21"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
       <c r="L3" s="22"/>
       <c r="M3" s="22"/>
       <c r="N3" s="2"/>
@@ -1129,28 +1055,28 @@
       <c r="Z3" s="3"/>
       <c r="AA3" s="3"/>
       <c r="AB3" s="3"/>
-      <c r="AC3" s="44"/>
-      <c r="AD3" s="44"/>
-      <c r="AE3" s="44"/>
-      <c r="AF3" s="44"/>
-      <c r="AG3" s="44"/>
-      <c r="AH3" s="44"/>
-      <c r="AI3" s="44"/>
-      <c r="AJ3" s="44"/>
-      <c r="AK3" s="44"/>
+      <c r="AC3" s="23"/>
+      <c r="AD3" s="23"/>
+      <c r="AE3" s="23"/>
+      <c r="AF3" s="23"/>
+      <c r="AG3" s="23"/>
+      <c r="AH3" s="23"/>
+      <c r="AI3" s="23"/>
+      <c r="AJ3" s="23"/>
+      <c r="AK3" s="23"/>
     </row>
     <row r="4" spans="1:54" s="19" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="27"/>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="27"/>
-      <c r="J4" s="27"/>
-      <c r="K4" s="27"/>
+      <c r="A4" s="21"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
       <c r="L4" s="22"/>
       <c r="M4" s="22"/>
       <c r="N4" s="2"/>
@@ -1164,34 +1090,32 @@
       <c r="V4" s="2"/>
       <c r="W4" s="2"/>
       <c r="X4" s="2"/>
-      <c r="Y4" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z4" s="27"/>
-      <c r="AA4" s="27"/>
-      <c r="AB4" s="27"/>
-      <c r="AC4" s="27"/>
-      <c r="AD4" s="27"/>
-      <c r="AE4" s="27"/>
-      <c r="AF4" s="27"/>
-      <c r="AG4" s="27"/>
-      <c r="AH4" s="27"/>
-      <c r="AI4" s="27"/>
-      <c r="AJ4" s="27"/>
-      <c r="AK4" s="27"/>
+      <c r="Y4" s="21"/>
+      <c r="Z4" s="21"/>
+      <c r="AA4" s="21"/>
+      <c r="AB4" s="21"/>
+      <c r="AC4" s="21"/>
+      <c r="AD4" s="21"/>
+      <c r="AE4" s="21"/>
+      <c r="AF4" s="21"/>
+      <c r="AG4" s="21"/>
+      <c r="AH4" s="21"/>
+      <c r="AI4" s="21"/>
+      <c r="AJ4" s="21"/>
+      <c r="AK4" s="21"/>
     </row>
     <row r="5" spans="1:54" s="19" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="27"/>
-      <c r="B5" s="27"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
-      <c r="I5" s="27"/>
-      <c r="J5" s="27"/>
-      <c r="K5" s="27"/>
+      <c r="A5" s="21"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="21"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="21"/>
       <c r="L5" s="22"/>
       <c r="M5" s="22"/>
       <c r="N5" s="2"/>
@@ -1205,19 +1129,19 @@
       <c r="V5" s="2"/>
       <c r="W5" s="2"/>
       <c r="X5" s="2"/>
-      <c r="Y5" s="27"/>
-      <c r="Z5" s="27"/>
-      <c r="AA5" s="27"/>
-      <c r="AB5" s="27"/>
-      <c r="AC5" s="27"/>
-      <c r="AD5" s="27"/>
-      <c r="AE5" s="27"/>
-      <c r="AF5" s="27"/>
-      <c r="AG5" s="27"/>
-      <c r="AH5" s="27"/>
-      <c r="AI5" s="27"/>
-      <c r="AJ5" s="27"/>
-      <c r="AK5" s="27"/>
+      <c r="Y5" s="21"/>
+      <c r="Z5" s="21"/>
+      <c r="AA5" s="21"/>
+      <c r="AB5" s="21"/>
+      <c r="AC5" s="21"/>
+      <c r="AD5" s="21"/>
+      <c r="AE5" s="21"/>
+      <c r="AF5" s="21"/>
+      <c r="AG5" s="21"/>
+      <c r="AH5" s="21"/>
+      <c r="AI5" s="21"/>
+      <c r="AJ5" s="21"/>
+      <c r="AK5" s="21"/>
     </row>
     <row r="6" spans="1:54" s="19" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="2"/>
@@ -1249,16 +1173,14 @@
       <c r="AA6" s="3"/>
       <c r="AB6" s="3"/>
       <c r="AC6" s="3"/>
-      <c r="AD6" s="27">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="27"/>
-      <c r="AF6" s="27"/>
-      <c r="AG6" s="27"/>
-      <c r="AH6" s="27"/>
-      <c r="AI6" s="27"/>
-      <c r="AJ6" s="27"/>
-      <c r="AK6" s="27"/>
+      <c r="AD6" s="21"/>
+      <c r="AE6" s="21"/>
+      <c r="AF6" s="21"/>
+      <c r="AG6" s="21"/>
+      <c r="AH6" s="21"/>
+      <c r="AI6" s="21"/>
+      <c r="AJ6" s="21"/>
+      <c r="AK6" s="21"/>
     </row>
     <row r="7" spans="1:54" s="19" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="2"/>
@@ -1290,14 +1212,14 @@
       <c r="AA7" s="3"/>
       <c r="AB7" s="3"/>
       <c r="AC7" s="3"/>
-      <c r="AD7" s="27"/>
-      <c r="AE7" s="27"/>
-      <c r="AF7" s="27"/>
-      <c r="AG7" s="27"/>
-      <c r="AH7" s="27"/>
-      <c r="AI7" s="27"/>
-      <c r="AJ7" s="27"/>
-      <c r="AK7" s="27"/>
+      <c r="AD7" s="21"/>
+      <c r="AE7" s="21"/>
+      <c r="AF7" s="21"/>
+      <c r="AG7" s="21"/>
+      <c r="AH7" s="21"/>
+      <c r="AI7" s="21"/>
+      <c r="AJ7" s="21"/>
+      <c r="AK7" s="21"/>
     </row>
     <row r="8" spans="1:54" s="19" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="2"/>
@@ -1339,84 +1261,84 @@
       <c r="AK8" s="2"/>
     </row>
     <row r="9" spans="1:54" s="19" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="39" t="s">
-        <v>3</v>
+      <c r="A9" s="24" t="s">
+        <v>1</v>
       </c>
-      <c r="B9" s="39"/>
-      <c r="C9" s="39"/>
-      <c r="D9" s="39"/>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="39"/>
-      <c r="H9" s="39"/>
-      <c r="I9" s="39"/>
-      <c r="J9" s="39"/>
-      <c r="K9" s="39"/>
-      <c r="L9" s="39"/>
-      <c r="M9" s="39"/>
-      <c r="N9" s="39"/>
-      <c r="O9" s="39"/>
-      <c r="P9" s="39"/>
-      <c r="Q9" s="39"/>
-      <c r="R9" s="39"/>
-      <c r="S9" s="39"/>
-      <c r="T9" s="39"/>
-      <c r="U9" s="39"/>
-      <c r="V9" s="39"/>
-      <c r="W9" s="39"/>
-      <c r="X9" s="39"/>
-      <c r="Y9" s="39"/>
-      <c r="Z9" s="39"/>
-      <c r="AA9" s="39"/>
-      <c r="AB9" s="39"/>
-      <c r="AC9" s="39"/>
-      <c r="AD9" s="39"/>
-      <c r="AE9" s="39"/>
-      <c r="AF9" s="39"/>
-      <c r="AG9" s="39"/>
-      <c r="AH9" s="39"/>
-      <c r="AI9" s="39"/>
-      <c r="AJ9" s="39"/>
-      <c r="AK9" s="39"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="24"/>
+      <c r="I9" s="24"/>
+      <c r="J9" s="24"/>
+      <c r="K9" s="24"/>
+      <c r="L9" s="24"/>
+      <c r="M9" s="24"/>
+      <c r="N9" s="24"/>
+      <c r="O9" s="24"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="24"/>
+      <c r="R9" s="24"/>
+      <c r="S9" s="24"/>
+      <c r="T9" s="24"/>
+      <c r="U9" s="24"/>
+      <c r="V9" s="24"/>
+      <c r="W9" s="24"/>
+      <c r="X9" s="24"/>
+      <c r="Y9" s="24"/>
+      <c r="Z9" s="24"/>
+      <c r="AA9" s="24"/>
+      <c r="AB9" s="24"/>
+      <c r="AC9" s="24"/>
+      <c r="AD9" s="24"/>
+      <c r="AE9" s="24"/>
+      <c r="AF9" s="24"/>
+      <c r="AG9" s="24"/>
+      <c r="AH9" s="24"/>
+      <c r="AI9" s="24"/>
+      <c r="AJ9" s="24"/>
+      <c r="AK9" s="24"/>
     </row>
     <row r="10" spans="1:54" s="19" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="40"/>
-      <c r="B10" s="40"/>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="40"/>
-      <c r="I10" s="40"/>
-      <c r="J10" s="40"/>
-      <c r="K10" s="40"/>
-      <c r="L10" s="40"/>
-      <c r="M10" s="40"/>
-      <c r="N10" s="40"/>
-      <c r="O10" s="40"/>
-      <c r="P10" s="40"/>
-      <c r="Q10" s="40"/>
-      <c r="R10" s="40"/>
-      <c r="S10" s="40"/>
-      <c r="T10" s="40"/>
-      <c r="U10" s="40"/>
-      <c r="V10" s="40"/>
-      <c r="W10" s="40"/>
-      <c r="X10" s="40"/>
-      <c r="Y10" s="40"/>
-      <c r="Z10" s="40"/>
-      <c r="AA10" s="40"/>
-      <c r="AB10" s="40"/>
-      <c r="AC10" s="40"/>
-      <c r="AD10" s="40"/>
-      <c r="AE10" s="40"/>
-      <c r="AF10" s="40"/>
-      <c r="AG10" s="40"/>
-      <c r="AH10" s="40"/>
-      <c r="AI10" s="40"/>
-      <c r="AJ10" s="40"/>
-      <c r="AK10" s="40"/>
+      <c r="A10" s="25"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="25"/>
+      <c r="L10" s="25"/>
+      <c r="M10" s="25"/>
+      <c r="N10" s="25"/>
+      <c r="O10" s="25"/>
+      <c r="P10" s="25"/>
+      <c r="Q10" s="25"/>
+      <c r="R10" s="25"/>
+      <c r="S10" s="25"/>
+      <c r="T10" s="25"/>
+      <c r="U10" s="25"/>
+      <c r="V10" s="25"/>
+      <c r="W10" s="25"/>
+      <c r="X10" s="25"/>
+      <c r="Y10" s="25"/>
+      <c r="Z10" s="25"/>
+      <c r="AA10" s="25"/>
+      <c r="AB10" s="25"/>
+      <c r="AC10" s="25"/>
+      <c r="AD10" s="25"/>
+      <c r="AE10" s="25"/>
+      <c r="AF10" s="25"/>
+      <c r="AG10" s="25"/>
+      <c r="AH10" s="25"/>
+      <c r="AI10" s="25"/>
+      <c r="AJ10" s="25"/>
+      <c r="AK10" s="25"/>
     </row>
     <row r="11" spans="1:54" s="19" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="5"/>
@@ -1458,202 +1380,202 @@
       <c r="AK11" s="5"/>
     </row>
     <row r="12" spans="1:54" s="19" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="41" t="s">
-        <v>4</v>
+      <c r="A12" s="26" t="s">
+        <v>2</v>
       </c>
-      <c r="B12" s="41"/>
-      <c r="C12" s="41"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="41"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="41"/>
-      <c r="I12" s="41"/>
-      <c r="J12" s="41"/>
-      <c r="K12" s="41"/>
-      <c r="L12" s="41"/>
-      <c r="M12" s="41"/>
-      <c r="N12" s="41"/>
-      <c r="O12" s="41"/>
-      <c r="P12" s="41"/>
-      <c r="Q12" s="41"/>
-      <c r="R12" s="41"/>
-      <c r="S12" s="41"/>
-      <c r="T12" s="41"/>
-      <c r="U12" s="41"/>
-      <c r="V12" s="41"/>
-      <c r="W12" s="41"/>
-      <c r="X12" s="41"/>
-      <c r="Y12" s="41"/>
-      <c r="Z12" s="41"/>
-      <c r="AA12" s="41"/>
-      <c r="AB12" s="41"/>
-      <c r="AC12" s="41"/>
-      <c r="AD12" s="41"/>
-      <c r="AE12" s="41"/>
-      <c r="AF12" s="41"/>
-      <c r="AG12" s="41"/>
-      <c r="AH12" s="41"/>
-      <c r="AI12" s="41"/>
-      <c r="AJ12" s="41"/>
-      <c r="AK12" s="41"/>
+      <c r="B12" s="26"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="26"/>
+      <c r="I12" s="26"/>
+      <c r="J12" s="26"/>
+      <c r="K12" s="26"/>
+      <c r="L12" s="26"/>
+      <c r="M12" s="26"/>
+      <c r="N12" s="26"/>
+      <c r="O12" s="26"/>
+      <c r="P12" s="26"/>
+      <c r="Q12" s="26"/>
+      <c r="R12" s="26"/>
+      <c r="S12" s="26"/>
+      <c r="T12" s="26"/>
+      <c r="U12" s="26"/>
+      <c r="V12" s="26"/>
+      <c r="W12" s="26"/>
+      <c r="X12" s="26"/>
+      <c r="Y12" s="26"/>
+      <c r="Z12" s="26"/>
+      <c r="AA12" s="26"/>
+      <c r="AB12" s="26"/>
+      <c r="AC12" s="26"/>
+      <c r="AD12" s="26"/>
+      <c r="AE12" s="26"/>
+      <c r="AF12" s="26"/>
+      <c r="AG12" s="26"/>
+      <c r="AH12" s="26"/>
+      <c r="AI12" s="26"/>
+      <c r="AJ12" s="26"/>
+      <c r="AK12" s="26"/>
     </row>
     <row r="13" spans="1:54" s="19" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="41"/>
-      <c r="B13" s="41"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="41"/>
-      <c r="I13" s="41"/>
-      <c r="J13" s="41"/>
-      <c r="K13" s="41"/>
-      <c r="L13" s="41"/>
-      <c r="M13" s="41"/>
-      <c r="N13" s="41"/>
-      <c r="O13" s="41"/>
-      <c r="P13" s="41"/>
-      <c r="Q13" s="41"/>
-      <c r="R13" s="41"/>
-      <c r="S13" s="41"/>
-      <c r="T13" s="41"/>
-      <c r="U13" s="41"/>
-      <c r="V13" s="41"/>
-      <c r="W13" s="41"/>
-      <c r="X13" s="41"/>
-      <c r="Y13" s="41"/>
-      <c r="Z13" s="41"/>
-      <c r="AA13" s="41"/>
-      <c r="AB13" s="41"/>
-      <c r="AC13" s="41"/>
-      <c r="AD13" s="41"/>
-      <c r="AE13" s="41"/>
-      <c r="AF13" s="41"/>
-      <c r="AG13" s="41"/>
-      <c r="AH13" s="41"/>
-      <c r="AI13" s="41"/>
-      <c r="AJ13" s="41"/>
-      <c r="AK13" s="41"/>
+      <c r="A13" s="26"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="26"/>
+      <c r="I13" s="26"/>
+      <c r="J13" s="26"/>
+      <c r="K13" s="26"/>
+      <c r="L13" s="26"/>
+      <c r="M13" s="26"/>
+      <c r="N13" s="26"/>
+      <c r="O13" s="26"/>
+      <c r="P13" s="26"/>
+      <c r="Q13" s="26"/>
+      <c r="R13" s="26"/>
+      <c r="S13" s="26"/>
+      <c r="T13" s="26"/>
+      <c r="U13" s="26"/>
+      <c r="V13" s="26"/>
+      <c r="W13" s="26"/>
+      <c r="X13" s="26"/>
+      <c r="Y13" s="26"/>
+      <c r="Z13" s="26"/>
+      <c r="AA13" s="26"/>
+      <c r="AB13" s="26"/>
+      <c r="AC13" s="26"/>
+      <c r="AD13" s="26"/>
+      <c r="AE13" s="26"/>
+      <c r="AF13" s="26"/>
+      <c r="AG13" s="26"/>
+      <c r="AH13" s="26"/>
+      <c r="AI13" s="26"/>
+      <c r="AJ13" s="26"/>
+      <c r="AK13" s="26"/>
     </row>
     <row r="14" spans="1:54" s="19" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="41"/>
-      <c r="B14" s="41"/>
-      <c r="C14" s="41"/>
-      <c r="D14" s="41"/>
-      <c r="E14" s="41"/>
-      <c r="F14" s="41"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="41"/>
-      <c r="I14" s="41"/>
-      <c r="J14" s="41"/>
-      <c r="K14" s="41"/>
-      <c r="L14" s="41"/>
-      <c r="M14" s="41"/>
-      <c r="N14" s="41"/>
-      <c r="O14" s="41"/>
-      <c r="P14" s="41"/>
-      <c r="Q14" s="41"/>
-      <c r="R14" s="41"/>
-      <c r="S14" s="41"/>
-      <c r="T14" s="41"/>
-      <c r="U14" s="41"/>
-      <c r="V14" s="41"/>
-      <c r="W14" s="41"/>
-      <c r="X14" s="41"/>
-      <c r="Y14" s="41"/>
-      <c r="Z14" s="41"/>
-      <c r="AA14" s="41"/>
-      <c r="AB14" s="41"/>
-      <c r="AC14" s="41"/>
-      <c r="AD14" s="41"/>
-      <c r="AE14" s="41"/>
-      <c r="AF14" s="41"/>
-      <c r="AG14" s="41"/>
-      <c r="AH14" s="41"/>
-      <c r="AI14" s="41"/>
-      <c r="AJ14" s="41"/>
-      <c r="AK14" s="41"/>
+      <c r="A14" s="26"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="26"/>
+      <c r="I14" s="26"/>
+      <c r="J14" s="26"/>
+      <c r="K14" s="26"/>
+      <c r="L14" s="26"/>
+      <c r="M14" s="26"/>
+      <c r="N14" s="26"/>
+      <c r="O14" s="26"/>
+      <c r="P14" s="26"/>
+      <c r="Q14" s="26"/>
+      <c r="R14" s="26"/>
+      <c r="S14" s="26"/>
+      <c r="T14" s="26"/>
+      <c r="U14" s="26"/>
+      <c r="V14" s="26"/>
+      <c r="W14" s="26"/>
+      <c r="X14" s="26"/>
+      <c r="Y14" s="26"/>
+      <c r="Z14" s="26"/>
+      <c r="AA14" s="26"/>
+      <c r="AB14" s="26"/>
+      <c r="AC14" s="26"/>
+      <c r="AD14" s="26"/>
+      <c r="AE14" s="26"/>
+      <c r="AF14" s="26"/>
+      <c r="AG14" s="26"/>
+      <c r="AH14" s="26"/>
+      <c r="AI14" s="26"/>
+      <c r="AJ14" s="26"/>
+      <c r="AK14" s="26"/>
     </row>
     <row r="15" spans="1:54" s="19" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="41"/>
-      <c r="B15" s="41"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="41"/>
-      <c r="I15" s="41"/>
-      <c r="J15" s="41"/>
-      <c r="K15" s="41"/>
-      <c r="L15" s="41"/>
-      <c r="M15" s="41"/>
-      <c r="N15" s="41"/>
-      <c r="O15" s="41"/>
-      <c r="P15" s="41"/>
-      <c r="Q15" s="41"/>
-      <c r="R15" s="41"/>
-      <c r="S15" s="41"/>
-      <c r="T15" s="41"/>
-      <c r="U15" s="41"/>
-      <c r="V15" s="41"/>
-      <c r="W15" s="41"/>
-      <c r="X15" s="41"/>
-      <c r="Y15" s="41"/>
-      <c r="Z15" s="41"/>
-      <c r="AA15" s="41"/>
-      <c r="AB15" s="41"/>
-      <c r="AC15" s="41"/>
-      <c r="AD15" s="41"/>
-      <c r="AE15" s="41"/>
-      <c r="AF15" s="41"/>
-      <c r="AG15" s="41"/>
-      <c r="AH15" s="41"/>
-      <c r="AI15" s="41"/>
-      <c r="AJ15" s="41"/>
-      <c r="AK15" s="41"/>
+      <c r="A15" s="26"/>
+      <c r="B15" s="26"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="26"/>
+      <c r="I15" s="26"/>
+      <c r="J15" s="26"/>
+      <c r="K15" s="26"/>
+      <c r="L15" s="26"/>
+      <c r="M15" s="26"/>
+      <c r="N15" s="26"/>
+      <c r="O15" s="26"/>
+      <c r="P15" s="26"/>
+      <c r="Q15" s="26"/>
+      <c r="R15" s="26"/>
+      <c r="S15" s="26"/>
+      <c r="T15" s="26"/>
+      <c r="U15" s="26"/>
+      <c r="V15" s="26"/>
+      <c r="W15" s="26"/>
+      <c r="X15" s="26"/>
+      <c r="Y15" s="26"/>
+      <c r="Z15" s="26"/>
+      <c r="AA15" s="26"/>
+      <c r="AB15" s="26"/>
+      <c r="AC15" s="26"/>
+      <c r="AD15" s="26"/>
+      <c r="AE15" s="26"/>
+      <c r="AF15" s="26"/>
+      <c r="AG15" s="26"/>
+      <c r="AH15" s="26"/>
+      <c r="AI15" s="26"/>
+      <c r="AJ15" s="26"/>
+      <c r="AK15" s="26"/>
       <c r="BB15" s="20"/>
     </row>
     <row r="16" spans="1:54" s="19" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="41"/>
-      <c r="B16" s="41"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="41"/>
-      <c r="I16" s="41"/>
-      <c r="J16" s="41"/>
-      <c r="K16" s="41"/>
-      <c r="L16" s="41"/>
-      <c r="M16" s="41"/>
-      <c r="N16" s="41"/>
-      <c r="O16" s="41"/>
-      <c r="P16" s="41"/>
-      <c r="Q16" s="41"/>
-      <c r="R16" s="41"/>
-      <c r="S16" s="41"/>
-      <c r="T16" s="41"/>
-      <c r="U16" s="41"/>
-      <c r="V16" s="41"/>
-      <c r="W16" s="41"/>
-      <c r="X16" s="41"/>
-      <c r="Y16" s="41"/>
-      <c r="Z16" s="41"/>
-      <c r="AA16" s="41"/>
-      <c r="AB16" s="41"/>
-      <c r="AC16" s="41"/>
-      <c r="AD16" s="41"/>
-      <c r="AE16" s="41"/>
-      <c r="AF16" s="41"/>
-      <c r="AG16" s="41"/>
-      <c r="AH16" s="41"/>
-      <c r="AI16" s="41"/>
-      <c r="AJ16" s="41"/>
-      <c r="AK16" s="41"/>
+      <c r="A16" s="26"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="26"/>
+      <c r="J16" s="26"/>
+      <c r="K16" s="26"/>
+      <c r="L16" s="26"/>
+      <c r="M16" s="26"/>
+      <c r="N16" s="26"/>
+      <c r="O16" s="26"/>
+      <c r="P16" s="26"/>
+      <c r="Q16" s="26"/>
+      <c r="R16" s="26"/>
+      <c r="S16" s="26"/>
+      <c r="T16" s="26"/>
+      <c r="U16" s="26"/>
+      <c r="V16" s="26"/>
+      <c r="W16" s="26"/>
+      <c r="X16" s="26"/>
+      <c r="Y16" s="26"/>
+      <c r="Z16" s="26"/>
+      <c r="AA16" s="26"/>
+      <c r="AB16" s="26"/>
+      <c r="AC16" s="26"/>
+      <c r="AD16" s="26"/>
+      <c r="AE16" s="26"/>
+      <c r="AF16" s="26"/>
+      <c r="AG16" s="26"/>
+      <c r="AH16" s="26"/>
+      <c r="AI16" s="26"/>
+      <c r="AJ16" s="26"/>
+      <c r="AK16" s="26"/>
       <c r="BB16" s="20"/>
     </row>
     <row r="17" spans="1:54" s="19" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
@@ -1736,98 +1658,94 @@
       <c r="AK18" s="2"/>
     </row>
     <row r="19" spans="1:54" s="19" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="J19" s="27"/>
+      <c r="K19" s="27"/>
+      <c r="L19" s="27"/>
+      <c r="M19" s="27"/>
+      <c r="N19" s="28"/>
+      <c r="O19" s="28"/>
+      <c r="P19" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="27"/>
-      <c r="I19" s="42" t="s">
+      <c r="Q19" s="27"/>
+      <c r="R19" s="28"/>
+      <c r="S19" s="28"/>
+      <c r="T19" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="J19" s="42"/>
-      <c r="K19" s="42"/>
-      <c r="L19" s="42"/>
-      <c r="M19" s="42"/>
-      <c r="N19" s="30"/>
-      <c r="O19" s="30"/>
-      <c r="P19" s="42" t="s">
+      <c r="U19" s="27"/>
+      <c r="V19" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="Q19" s="42"/>
-      <c r="R19" s="30"/>
-      <c r="S19" s="30"/>
-      <c r="T19" s="42" t="s">
+      <c r="W19" s="28"/>
+      <c r="X19" s="28"/>
+      <c r="Y19" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="U19" s="42"/>
-      <c r="V19" s="43" t="s">
+      <c r="Z19" s="28"/>
+      <c r="AA19" s="28"/>
+      <c r="AB19" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="W19" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="X19" s="30"/>
-      <c r="Y19" s="30" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z19" s="30"/>
-      <c r="AA19" s="30"/>
-      <c r="AB19" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="AC19" s="28"/>
-      <c r="AD19" s="28"/>
-      <c r="AE19" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="AF19" s="38"/>
-      <c r="AG19" s="38"/>
-      <c r="AH19" s="38"/>
-      <c r="AI19" s="38"/>
+      <c r="AC19" s="30"/>
+      <c r="AD19" s="30"/>
+      <c r="AE19" s="31"/>
+      <c r="AF19" s="31"/>
+      <c r="AG19" s="31"/>
+      <c r="AH19" s="31"/>
+      <c r="AI19" s="31"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
     </row>
     <row r="20" spans="1:54" s="19" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="27"/>
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="27"/>
-      <c r="I20" s="42"/>
-      <c r="J20" s="42"/>
-      <c r="K20" s="42"/>
-      <c r="L20" s="42"/>
-      <c r="M20" s="42"/>
-      <c r="N20" s="30"/>
-      <c r="O20" s="30"/>
-      <c r="P20" s="42"/>
-      <c r="Q20" s="42"/>
-      <c r="R20" s="30"/>
-      <c r="S20" s="30"/>
-      <c r="T20" s="42"/>
-      <c r="U20" s="42"/>
-      <c r="V20" s="43"/>
-      <c r="W20" s="30"/>
-      <c r="X20" s="30"/>
-      <c r="Y20" s="30"/>
-      <c r="Z20" s="30"/>
-      <c r="AA20" s="30"/>
-      <c r="AB20" s="28"/>
-      <c r="AC20" s="28"/>
-      <c r="AD20" s="28"/>
-      <c r="AE20" s="38"/>
-      <c r="AF20" s="38"/>
-      <c r="AG20" s="38"/>
-      <c r="AH20" s="38"/>
-      <c r="AI20" s="38"/>
+      <c r="A20" s="21"/>
+      <c r="B20" s="21"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="27"/>
+      <c r="J20" s="27"/>
+      <c r="K20" s="27"/>
+      <c r="L20" s="27"/>
+      <c r="M20" s="27"/>
+      <c r="N20" s="28"/>
+      <c r="O20" s="28"/>
+      <c r="P20" s="27"/>
+      <c r="Q20" s="27"/>
+      <c r="R20" s="28"/>
+      <c r="S20" s="28"/>
+      <c r="T20" s="27"/>
+      <c r="U20" s="27"/>
+      <c r="V20" s="29"/>
+      <c r="W20" s="28"/>
+      <c r="X20" s="28"/>
+      <c r="Y20" s="28"/>
+      <c r="Z20" s="28"/>
+      <c r="AA20" s="28"/>
+      <c r="AB20" s="30"/>
+      <c r="AC20" s="30"/>
+      <c r="AD20" s="30"/>
+      <c r="AE20" s="31"/>
+      <c r="AF20" s="31"/>
+      <c r="AG20" s="31"/>
+      <c r="AH20" s="31"/>
+      <c r="AI20" s="31"/>
       <c r="AJ20" s="3"/>
       <c r="AK20" s="3"/>
     </row>
@@ -1871,86 +1789,84 @@
       <c r="AK21" s="7"/>
     </row>
     <row r="22" spans="1:54" s="19" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="27" t="s">
-        <v>14</v>
+      <c r="A22" s="21" t="s">
+        <v>10</v>
       </c>
-      <c r="B22" s="27"/>
-      <c r="C22" s="27"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="27"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="27"/>
-      <c r="H22" s="27"/>
-      <c r="I22" s="30" t="s">
-        <v>15</v>
-      </c>
-      <c r="J22" s="30"/>
-      <c r="K22" s="30"/>
-      <c r="L22" s="30"/>
-      <c r="M22" s="30"/>
-      <c r="N22" s="30"/>
-      <c r="O22" s="30"/>
-      <c r="P22" s="30"/>
-      <c r="Q22" s="30"/>
-      <c r="R22" s="30"/>
-      <c r="S22" s="30"/>
-      <c r="T22" s="30"/>
-      <c r="U22" s="30"/>
-      <c r="V22" s="30"/>
-      <c r="W22" s="30"/>
-      <c r="X22" s="30"/>
-      <c r="Y22" s="30"/>
-      <c r="Z22" s="30"/>
-      <c r="AA22" s="30"/>
-      <c r="AB22" s="30"/>
-      <c r="AC22" s="30"/>
-      <c r="AD22" s="30"/>
-      <c r="AE22" s="30"/>
-      <c r="AF22" s="30"/>
-      <c r="AG22" s="30"/>
-      <c r="AH22" s="30"/>
-      <c r="AI22" s="30"/>
-      <c r="AJ22" s="30"/>
-      <c r="AK22" s="30"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="28"/>
+      <c r="J22" s="28"/>
+      <c r="K22" s="28"/>
+      <c r="L22" s="28"/>
+      <c r="M22" s="28"/>
+      <c r="N22" s="28"/>
+      <c r="O22" s="28"/>
+      <c r="P22" s="28"/>
+      <c r="Q22" s="28"/>
+      <c r="R22" s="28"/>
+      <c r="S22" s="28"/>
+      <c r="T22" s="28"/>
+      <c r="U22" s="28"/>
+      <c r="V22" s="28"/>
+      <c r="W22" s="28"/>
+      <c r="X22" s="28"/>
+      <c r="Y22" s="28"/>
+      <c r="Z22" s="28"/>
+      <c r="AA22" s="28"/>
+      <c r="AB22" s="28"/>
+      <c r="AC22" s="28"/>
+      <c r="AD22" s="28"/>
+      <c r="AE22" s="28"/>
+      <c r="AF22" s="28"/>
+      <c r="AG22" s="28"/>
+      <c r="AH22" s="28"/>
+      <c r="AI22" s="28"/>
+      <c r="AJ22" s="28"/>
+      <c r="AK22" s="28"/>
     </row>
     <row r="23" spans="1:54" s="19" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="27"/>
-      <c r="B23" s="27"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="27"/>
-      <c r="I23" s="31"/>
-      <c r="J23" s="31"/>
-      <c r="K23" s="31"/>
-      <c r="L23" s="31"/>
-      <c r="M23" s="31"/>
-      <c r="N23" s="31"/>
-      <c r="O23" s="31"/>
-      <c r="P23" s="31"/>
-      <c r="Q23" s="31"/>
-      <c r="R23" s="31"/>
-      <c r="S23" s="31"/>
-      <c r="T23" s="31"/>
-      <c r="U23" s="31"/>
-      <c r="V23" s="31"/>
-      <c r="W23" s="31"/>
-      <c r="X23" s="31"/>
-      <c r="Y23" s="31"/>
-      <c r="Z23" s="31"/>
-      <c r="AA23" s="31"/>
-      <c r="AB23" s="31"/>
-      <c r="AC23" s="31"/>
-      <c r="AD23" s="31"/>
-      <c r="AE23" s="31"/>
-      <c r="AF23" s="31"/>
-      <c r="AG23" s="31"/>
-      <c r="AH23" s="31"/>
-      <c r="AI23" s="31"/>
-      <c r="AJ23" s="31"/>
-      <c r="AK23" s="31"/>
+      <c r="A23" s="21"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="32"/>
+      <c r="J23" s="32"/>
+      <c r="K23" s="32"/>
+      <c r="L23" s="32"/>
+      <c r="M23" s="32"/>
+      <c r="N23" s="32"/>
+      <c r="O23" s="32"/>
+      <c r="P23" s="32"/>
+      <c r="Q23" s="32"/>
+      <c r="R23" s="32"/>
+      <c r="S23" s="32"/>
+      <c r="T23" s="32"/>
+      <c r="U23" s="32"/>
+      <c r="V23" s="32"/>
+      <c r="W23" s="32"/>
+      <c r="X23" s="32"/>
+      <c r="Y23" s="32"/>
+      <c r="Z23" s="32"/>
+      <c r="AA23" s="32"/>
+      <c r="AB23" s="32"/>
+      <c r="AC23" s="32"/>
+      <c r="AD23" s="32"/>
+      <c r="AE23" s="32"/>
+      <c r="AF23" s="32"/>
+      <c r="AG23" s="32"/>
+      <c r="AH23" s="32"/>
+      <c r="AI23" s="32"/>
+      <c r="AJ23" s="32"/>
+      <c r="AK23" s="32"/>
     </row>
     <row r="24" spans="1:54" s="19" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="7"/>
@@ -1992,38 +1908,36 @@
       <c r="AK24" s="2"/>
     </row>
     <row r="25" spans="1:54" s="19" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="27" t="s">
-        <v>16</v>
+      <c r="A25" s="21" t="s">
+        <v>11</v>
       </c>
-      <c r="B25" s="27"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="27"/>
-      <c r="H25" s="27"/>
-      <c r="I25" s="28">
-        <v>0</v>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="30"/>
+      <c r="J25" s="30"/>
+      <c r="K25" s="30"/>
+      <c r="L25" s="30"/>
+      <c r="M25" s="30"/>
+      <c r="N25" s="30"/>
+      <c r="O25" s="30"/>
+      <c r="P25" s="30"/>
+      <c r="Q25" s="30"/>
+      <c r="R25" s="30"/>
+      <c r="S25" s="30"/>
+      <c r="T25" s="30"/>
+      <c r="U25" s="30"/>
+      <c r="V25" s="30"/>
+      <c r="W25" s="30"/>
+      <c r="X25" s="30"/>
+      <c r="Y25" s="28" t="s">
+        <v>12</v>
       </c>
-      <c r="J25" s="28"/>
-      <c r="K25" s="28"/>
-      <c r="L25" s="28"/>
-      <c r="M25" s="28"/>
-      <c r="N25" s="28"/>
-      <c r="O25" s="28"/>
-      <c r="P25" s="28"/>
-      <c r="Q25" s="28"/>
-      <c r="R25" s="28"/>
-      <c r="S25" s="28"/>
-      <c r="T25" s="28"/>
-      <c r="U25" s="28"/>
-      <c r="V25" s="28"/>
-      <c r="W25" s="28"/>
-      <c r="X25" s="28"/>
-      <c r="Y25" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="Z25" s="30"/>
+      <c r="Z25" s="28"/>
       <c r="AA25" s="8"/>
       <c r="AB25" s="8"/>
       <c r="AC25" s="8"/>
@@ -2037,32 +1951,32 @@
       <c r="AK25" s="8"/>
     </row>
     <row r="26" spans="1:54" s="19" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="27"/>
-      <c r="B26" s="27"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="27"/>
-      <c r="E26" s="27"/>
-      <c r="F26" s="27"/>
-      <c r="G26" s="27"/>
-      <c r="H26" s="27"/>
-      <c r="I26" s="29"/>
-      <c r="J26" s="29"/>
-      <c r="K26" s="29"/>
-      <c r="L26" s="29"/>
-      <c r="M26" s="29"/>
-      <c r="N26" s="29"/>
-      <c r="O26" s="29"/>
-      <c r="P26" s="29"/>
-      <c r="Q26" s="29"/>
-      <c r="R26" s="29"/>
-      <c r="S26" s="29"/>
-      <c r="T26" s="29"/>
-      <c r="U26" s="29"/>
-      <c r="V26" s="29"/>
-      <c r="W26" s="29"/>
-      <c r="X26" s="29"/>
-      <c r="Y26" s="31"/>
-      <c r="Z26" s="31"/>
+      <c r="A26" s="21"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="38"/>
+      <c r="J26" s="38"/>
+      <c r="K26" s="38"/>
+      <c r="L26" s="38"/>
+      <c r="M26" s="38"/>
+      <c r="N26" s="38"/>
+      <c r="O26" s="38"/>
+      <c r="P26" s="38"/>
+      <c r="Q26" s="38"/>
+      <c r="R26" s="38"/>
+      <c r="S26" s="38"/>
+      <c r="T26" s="38"/>
+      <c r="U26" s="38"/>
+      <c r="V26" s="38"/>
+      <c r="W26" s="38"/>
+      <c r="X26" s="38"/>
+      <c r="Y26" s="32"/>
+      <c r="Z26" s="32"/>
       <c r="AA26" s="9"/>
       <c r="AB26" s="9"/>
       <c r="AC26" s="9"/>
@@ -2115,86 +2029,84 @@
       <c r="AK27" s="7"/>
     </row>
     <row r="28" spans="1:54" s="19" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="27" t="s">
-        <v>18</v>
+      <c r="A28" s="21" t="s">
+        <v>13</v>
       </c>
-      <c r="B28" s="27"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="27"/>
-      <c r="I28" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="J28" s="27"/>
-      <c r="K28" s="27"/>
-      <c r="L28" s="27"/>
-      <c r="M28" s="27"/>
-      <c r="N28" s="27"/>
-      <c r="O28" s="27"/>
-      <c r="P28" s="27"/>
-      <c r="Q28" s="27"/>
-      <c r="R28" s="27"/>
-      <c r="S28" s="27"/>
-      <c r="T28" s="27"/>
-      <c r="U28" s="27"/>
-      <c r="V28" s="27"/>
-      <c r="W28" s="27"/>
-      <c r="X28" s="27"/>
-      <c r="Y28" s="27"/>
-      <c r="Z28" s="27"/>
-      <c r="AA28" s="27"/>
-      <c r="AB28" s="27"/>
-      <c r="AC28" s="27"/>
-      <c r="AD28" s="27"/>
-      <c r="AE28" s="27"/>
-      <c r="AF28" s="27"/>
-      <c r="AG28" s="27"/>
-      <c r="AH28" s="27"/>
-      <c r="AI28" s="27"/>
-      <c r="AJ28" s="27"/>
-      <c r="AK28" s="27"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="21"/>
+      <c r="K28" s="21"/>
+      <c r="L28" s="21"/>
+      <c r="M28" s="21"/>
+      <c r="N28" s="21"/>
+      <c r="O28" s="21"/>
+      <c r="P28" s="21"/>
+      <c r="Q28" s="21"/>
+      <c r="R28" s="21"/>
+      <c r="S28" s="21"/>
+      <c r="T28" s="21"/>
+      <c r="U28" s="21"/>
+      <c r="V28" s="21"/>
+      <c r="W28" s="21"/>
+      <c r="X28" s="21"/>
+      <c r="Y28" s="21"/>
+      <c r="Z28" s="21"/>
+      <c r="AA28" s="21"/>
+      <c r="AB28" s="21"/>
+      <c r="AC28" s="21"/>
+      <c r="AD28" s="21"/>
+      <c r="AE28" s="21"/>
+      <c r="AF28" s="21"/>
+      <c r="AG28" s="21"/>
+      <c r="AH28" s="21"/>
+      <c r="AI28" s="21"/>
+      <c r="AJ28" s="21"/>
+      <c r="AK28" s="21"/>
     </row>
     <row r="29" spans="1:54" s="19" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="27"/>
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="27"/>
-      <c r="I29" s="32"/>
-      <c r="J29" s="32"/>
-      <c r="K29" s="32"/>
-      <c r="L29" s="32"/>
-      <c r="M29" s="32"/>
-      <c r="N29" s="32"/>
-      <c r="O29" s="32"/>
-      <c r="P29" s="32"/>
-      <c r="Q29" s="32"/>
-      <c r="R29" s="32"/>
-      <c r="S29" s="32"/>
-      <c r="T29" s="32"/>
-      <c r="U29" s="32"/>
-      <c r="V29" s="32"/>
-      <c r="W29" s="32"/>
-      <c r="X29" s="32"/>
-      <c r="Y29" s="32"/>
-      <c r="Z29" s="32"/>
-      <c r="AA29" s="32"/>
-      <c r="AB29" s="32"/>
-      <c r="AC29" s="32"/>
-      <c r="AD29" s="32"/>
-      <c r="AE29" s="32"/>
-      <c r="AF29" s="32"/>
-      <c r="AG29" s="32"/>
-      <c r="AH29" s="32"/>
-      <c r="AI29" s="32"/>
-      <c r="AJ29" s="32"/>
-      <c r="AK29" s="32"/>
+      <c r="A29" s="21"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="21"/>
+      <c r="I29" s="39"/>
+      <c r="J29" s="39"/>
+      <c r="K29" s="39"/>
+      <c r="L29" s="39"/>
+      <c r="M29" s="39"/>
+      <c r="N29" s="39"/>
+      <c r="O29" s="39"/>
+      <c r="P29" s="39"/>
+      <c r="Q29" s="39"/>
+      <c r="R29" s="39"/>
+      <c r="S29" s="39"/>
+      <c r="T29" s="39"/>
+      <c r="U29" s="39"/>
+      <c r="V29" s="39"/>
+      <c r="W29" s="39"/>
+      <c r="X29" s="39"/>
+      <c r="Y29" s="39"/>
+      <c r="Z29" s="39"/>
+      <c r="AA29" s="39"/>
+      <c r="AB29" s="39"/>
+      <c r="AC29" s="39"/>
+      <c r="AD29" s="39"/>
+      <c r="AE29" s="39"/>
+      <c r="AF29" s="39"/>
+      <c r="AG29" s="39"/>
+      <c r="AH29" s="39"/>
+      <c r="AI29" s="39"/>
+      <c r="AJ29" s="39"/>
+      <c r="AK29" s="39"/>
     </row>
     <row r="30" spans="1:54" s="19" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="7"/>
@@ -2587,88 +2499,88 @@
       <c r="AK39" s="7"/>
     </row>
     <row r="40" spans="1:37" s="19" customFormat="1" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="33" t="s">
-        <v>20</v>
+      <c r="A40" s="40" t="s">
+        <v>14</v>
       </c>
-      <c r="B40" s="34"/>
-      <c r="C40" s="34"/>
-      <c r="D40" s="34"/>
-      <c r="E40" s="34"/>
-      <c r="F40" s="34"/>
-      <c r="G40" s="34"/>
-      <c r="H40" s="34"/>
-      <c r="I40" s="34"/>
-      <c r="J40" s="34"/>
-      <c r="K40" s="34"/>
-      <c r="L40" s="34"/>
-      <c r="M40" s="34"/>
-      <c r="N40" s="34"/>
-      <c r="O40" s="34"/>
-      <c r="P40" s="34"/>
-      <c r="Q40" s="34"/>
-      <c r="R40" s="34"/>
-      <c r="S40" s="34"/>
-      <c r="T40" s="34"/>
-      <c r="U40" s="34"/>
-      <c r="V40" s="34"/>
-      <c r="W40" s="34"/>
-      <c r="X40" s="34"/>
-      <c r="Y40" s="34"/>
-      <c r="Z40" s="34"/>
-      <c r="AA40" s="34"/>
-      <c r="AB40" s="34"/>
-      <c r="AC40" s="34"/>
-      <c r="AD40" s="34"/>
-      <c r="AE40" s="34"/>
-      <c r="AF40" s="34"/>
-      <c r="AG40" s="34"/>
-      <c r="AH40" s="34"/>
-      <c r="AI40" s="34"/>
-      <c r="AJ40" s="34"/>
-      <c r="AK40" s="35"/>
+      <c r="B40" s="41"/>
+      <c r="C40" s="41"/>
+      <c r="D40" s="41"/>
+      <c r="E40" s="41"/>
+      <c r="F40" s="41"/>
+      <c r="G40" s="41"/>
+      <c r="H40" s="41"/>
+      <c r="I40" s="41"/>
+      <c r="J40" s="41"/>
+      <c r="K40" s="41"/>
+      <c r="L40" s="41"/>
+      <c r="M40" s="41"/>
+      <c r="N40" s="41"/>
+      <c r="O40" s="41"/>
+      <c r="P40" s="41"/>
+      <c r="Q40" s="41"/>
+      <c r="R40" s="41"/>
+      <c r="S40" s="41"/>
+      <c r="T40" s="41"/>
+      <c r="U40" s="41"/>
+      <c r="V40" s="41"/>
+      <c r="W40" s="41"/>
+      <c r="X40" s="41"/>
+      <c r="Y40" s="41"/>
+      <c r="Z40" s="41"/>
+      <c r="AA40" s="41"/>
+      <c r="AB40" s="41"/>
+      <c r="AC40" s="41"/>
+      <c r="AD40" s="41"/>
+      <c r="AE40" s="41"/>
+      <c r="AF40" s="41"/>
+      <c r="AG40" s="41"/>
+      <c r="AH40" s="41"/>
+      <c r="AI40" s="41"/>
+      <c r="AJ40" s="41"/>
+      <c r="AK40" s="42"/>
     </row>
     <row r="41" spans="1:37" s="19" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="36"/>
-      <c r="B41" s="27"/>
-      <c r="C41" s="27"/>
-      <c r="D41" s="27"/>
-      <c r="E41" s="27"/>
-      <c r="F41" s="27"/>
-      <c r="G41" s="27"/>
-      <c r="H41" s="27"/>
-      <c r="I41" s="27"/>
-      <c r="J41" s="27"/>
-      <c r="K41" s="27"/>
-      <c r="L41" s="27"/>
-      <c r="M41" s="27"/>
-      <c r="N41" s="27"/>
-      <c r="O41" s="27"/>
-      <c r="P41" s="27"/>
-      <c r="Q41" s="27"/>
-      <c r="R41" s="27"/>
-      <c r="S41" s="27"/>
-      <c r="T41" s="27"/>
-      <c r="U41" s="27"/>
-      <c r="V41" s="27"/>
-      <c r="W41" s="27"/>
-      <c r="X41" s="27"/>
-      <c r="Y41" s="27"/>
-      <c r="Z41" s="27"/>
-      <c r="AA41" s="27"/>
-      <c r="AB41" s="27"/>
-      <c r="AC41" s="27"/>
-      <c r="AD41" s="27"/>
-      <c r="AE41" s="27"/>
-      <c r="AF41" s="27"/>
-      <c r="AG41" s="27"/>
-      <c r="AH41" s="27"/>
-      <c r="AI41" s="27"/>
-      <c r="AJ41" s="27"/>
-      <c r="AK41" s="37"/>
+      <c r="A41" s="43"/>
+      <c r="B41" s="21"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="21"/>
+      <c r="G41" s="21"/>
+      <c r="H41" s="21"/>
+      <c r="I41" s="21"/>
+      <c r="J41" s="21"/>
+      <c r="K41" s="21"/>
+      <c r="L41" s="21"/>
+      <c r="M41" s="21"/>
+      <c r="N41" s="21"/>
+      <c r="O41" s="21"/>
+      <c r="P41" s="21"/>
+      <c r="Q41" s="21"/>
+      <c r="R41" s="21"/>
+      <c r="S41" s="21"/>
+      <c r="T41" s="21"/>
+      <c r="U41" s="21"/>
+      <c r="V41" s="21"/>
+      <c r="W41" s="21"/>
+      <c r="X41" s="21"/>
+      <c r="Y41" s="21"/>
+      <c r="Z41" s="21"/>
+      <c r="AA41" s="21"/>
+      <c r="AB41" s="21"/>
+      <c r="AC41" s="21"/>
+      <c r="AD41" s="21"/>
+      <c r="AE41" s="21"/>
+      <c r="AF41" s="21"/>
+      <c r="AG41" s="21"/>
+      <c r="AH41" s="21"/>
+      <c r="AI41" s="21"/>
+      <c r="AJ41" s="21"/>
+      <c r="AK41" s="44"/>
     </row>
     <row r="42" spans="1:37" s="19" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="21" t="s">
-        <v>21</v>
+      <c r="A42" s="33" t="s">
+        <v>15</v>
       </c>
       <c r="B42" s="22"/>
       <c r="C42" s="22"/>
@@ -2705,10 +2617,10 @@
       <c r="AH42" s="22"/>
       <c r="AI42" s="22"/>
       <c r="AJ42" s="22"/>
-      <c r="AK42" s="23"/>
+      <c r="AK42" s="34"/>
     </row>
     <row r="43" spans="1:37" s="19" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="21"/>
+      <c r="A43" s="33"/>
       <c r="B43" s="22"/>
       <c r="C43" s="22"/>
       <c r="D43" s="22"/>
@@ -2744,87 +2656,87 @@
       <c r="AH43" s="22"/>
       <c r="AI43" s="22"/>
       <c r="AJ43" s="22"/>
-      <c r="AK43" s="23"/>
+      <c r="AK43" s="34"/>
     </row>
     <row r="44" spans="1:37" s="19" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="24" t="s">
-        <v>22</v>
+      <c r="A44" s="35" t="s">
+        <v>16</v>
       </c>
-      <c r="B44" s="25"/>
-      <c r="C44" s="25"/>
-      <c r="D44" s="25"/>
-      <c r="E44" s="25"/>
-      <c r="F44" s="25"/>
-      <c r="G44" s="25"/>
-      <c r="H44" s="25"/>
-      <c r="I44" s="25"/>
-      <c r="J44" s="25"/>
-      <c r="K44" s="25"/>
-      <c r="L44" s="25"/>
-      <c r="M44" s="25"/>
-      <c r="N44" s="25"/>
-      <c r="O44" s="25"/>
-      <c r="P44" s="25"/>
-      <c r="Q44" s="25"/>
-      <c r="R44" s="25"/>
-      <c r="S44" s="25"/>
-      <c r="T44" s="25"/>
-      <c r="U44" s="25"/>
-      <c r="V44" s="25"/>
-      <c r="W44" s="25"/>
-      <c r="X44" s="25"/>
-      <c r="Y44" s="25"/>
-      <c r="Z44" s="25"/>
-      <c r="AA44" s="25"/>
-      <c r="AB44" s="25"/>
-      <c r="AC44" s="25"/>
-      <c r="AD44" s="25"/>
-      <c r="AE44" s="25"/>
-      <c r="AF44" s="25"/>
-      <c r="AG44" s="25"/>
-      <c r="AH44" s="25"/>
-      <c r="AI44" s="25"/>
-      <c r="AJ44" s="25"/>
-      <c r="AK44" s="26"/>
+      <c r="B44" s="36"/>
+      <c r="C44" s="36"/>
+      <c r="D44" s="36"/>
+      <c r="E44" s="36"/>
+      <c r="F44" s="36"/>
+      <c r="G44" s="36"/>
+      <c r="H44" s="36"/>
+      <c r="I44" s="36"/>
+      <c r="J44" s="36"/>
+      <c r="K44" s="36"/>
+      <c r="L44" s="36"/>
+      <c r="M44" s="36"/>
+      <c r="N44" s="36"/>
+      <c r="O44" s="36"/>
+      <c r="P44" s="36"/>
+      <c r="Q44" s="36"/>
+      <c r="R44" s="36"/>
+      <c r="S44" s="36"/>
+      <c r="T44" s="36"/>
+      <c r="U44" s="36"/>
+      <c r="V44" s="36"/>
+      <c r="W44" s="36"/>
+      <c r="X44" s="36"/>
+      <c r="Y44" s="36"/>
+      <c r="Z44" s="36"/>
+      <c r="AA44" s="36"/>
+      <c r="AB44" s="36"/>
+      <c r="AC44" s="36"/>
+      <c r="AD44" s="36"/>
+      <c r="AE44" s="36"/>
+      <c r="AF44" s="36"/>
+      <c r="AG44" s="36"/>
+      <c r="AH44" s="36"/>
+      <c r="AI44" s="36"/>
+      <c r="AJ44" s="36"/>
+      <c r="AK44" s="37"/>
     </row>
     <row r="45" spans="1:37" s="19" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="24"/>
-      <c r="B45" s="25"/>
-      <c r="C45" s="25"/>
-      <c r="D45" s="25"/>
-      <c r="E45" s="25"/>
-      <c r="F45" s="25"/>
-      <c r="G45" s="25"/>
-      <c r="H45" s="25"/>
-      <c r="I45" s="25"/>
-      <c r="J45" s="25"/>
-      <c r="K45" s="25"/>
-      <c r="L45" s="25"/>
-      <c r="M45" s="25"/>
-      <c r="N45" s="25"/>
-      <c r="O45" s="25"/>
-      <c r="P45" s="25"/>
-      <c r="Q45" s="25"/>
-      <c r="R45" s="25"/>
-      <c r="S45" s="25"/>
-      <c r="T45" s="25"/>
-      <c r="U45" s="25"/>
-      <c r="V45" s="25"/>
-      <c r="W45" s="25"/>
-      <c r="X45" s="25"/>
-      <c r="Y45" s="25"/>
-      <c r="Z45" s="25"/>
-      <c r="AA45" s="25"/>
-      <c r="AB45" s="25"/>
-      <c r="AC45" s="25"/>
-      <c r="AD45" s="25"/>
-      <c r="AE45" s="25"/>
-      <c r="AF45" s="25"/>
-      <c r="AG45" s="25"/>
-      <c r="AH45" s="25"/>
-      <c r="AI45" s="25"/>
-      <c r="AJ45" s="25"/>
-      <c r="AK45" s="26"/>
+      <c r="A45" s="35"/>
+      <c r="B45" s="36"/>
+      <c r="C45" s="36"/>
+      <c r="D45" s="36"/>
+      <c r="E45" s="36"/>
+      <c r="F45" s="36"/>
+      <c r="G45" s="36"/>
+      <c r="H45" s="36"/>
+      <c r="I45" s="36"/>
+      <c r="J45" s="36"/>
+      <c r="K45" s="36"/>
+      <c r="L45" s="36"/>
+      <c r="M45" s="36"/>
+      <c r="N45" s="36"/>
+      <c r="O45" s="36"/>
+      <c r="P45" s="36"/>
+      <c r="Q45" s="36"/>
+      <c r="R45" s="36"/>
+      <c r="S45" s="36"/>
+      <c r="T45" s="36"/>
+      <c r="U45" s="36"/>
+      <c r="V45" s="36"/>
+      <c r="W45" s="36"/>
+      <c r="X45" s="36"/>
+      <c r="Y45" s="36"/>
+      <c r="Z45" s="36"/>
+      <c r="AA45" s="36"/>
+      <c r="AB45" s="36"/>
+      <c r="AC45" s="36"/>
+      <c r="AD45" s="36"/>
+      <c r="AE45" s="36"/>
+      <c r="AF45" s="36"/>
+      <c r="AG45" s="36"/>
+      <c r="AH45" s="36"/>
+      <c r="AI45" s="36"/>
+      <c r="AJ45" s="36"/>
+      <c r="AK45" s="37"/>
     </row>
     <row r="46" spans="1:37" s="19" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="10"/>
@@ -3139,84 +3051,84 @@
       <c r="AK53" s="11"/>
     </row>
     <row r="54" spans="1:37" s="19" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="24" t="s">
-        <v>23</v>
+      <c r="A54" s="35" t="s">
+        <v>17</v>
       </c>
-      <c r="B54" s="25"/>
-      <c r="C54" s="25"/>
-      <c r="D54" s="25"/>
-      <c r="E54" s="25"/>
-      <c r="F54" s="25"/>
-      <c r="G54" s="25"/>
-      <c r="H54" s="25"/>
-      <c r="I54" s="25"/>
-      <c r="J54" s="25"/>
-      <c r="K54" s="25"/>
-      <c r="L54" s="25"/>
-      <c r="M54" s="25"/>
-      <c r="N54" s="25"/>
-      <c r="O54" s="25"/>
-      <c r="P54" s="25"/>
-      <c r="Q54" s="25"/>
-      <c r="R54" s="25"/>
-      <c r="S54" s="25"/>
-      <c r="T54" s="25"/>
-      <c r="U54" s="25"/>
-      <c r="V54" s="25"/>
-      <c r="W54" s="25"/>
-      <c r="X54" s="25"/>
-      <c r="Y54" s="25"/>
-      <c r="Z54" s="25"/>
-      <c r="AA54" s="25"/>
-      <c r="AB54" s="25"/>
-      <c r="AC54" s="25"/>
-      <c r="AD54" s="25"/>
-      <c r="AE54" s="25"/>
-      <c r="AF54" s="25"/>
-      <c r="AG54" s="25"/>
-      <c r="AH54" s="25"/>
-      <c r="AI54" s="25"/>
-      <c r="AJ54" s="25"/>
-      <c r="AK54" s="26"/>
+      <c r="B54" s="36"/>
+      <c r="C54" s="36"/>
+      <c r="D54" s="36"/>
+      <c r="E54" s="36"/>
+      <c r="F54" s="36"/>
+      <c r="G54" s="36"/>
+      <c r="H54" s="36"/>
+      <c r="I54" s="36"/>
+      <c r="J54" s="36"/>
+      <c r="K54" s="36"/>
+      <c r="L54" s="36"/>
+      <c r="M54" s="36"/>
+      <c r="N54" s="36"/>
+      <c r="O54" s="36"/>
+      <c r="P54" s="36"/>
+      <c r="Q54" s="36"/>
+      <c r="R54" s="36"/>
+      <c r="S54" s="36"/>
+      <c r="T54" s="36"/>
+      <c r="U54" s="36"/>
+      <c r="V54" s="36"/>
+      <c r="W54" s="36"/>
+      <c r="X54" s="36"/>
+      <c r="Y54" s="36"/>
+      <c r="Z54" s="36"/>
+      <c r="AA54" s="36"/>
+      <c r="AB54" s="36"/>
+      <c r="AC54" s="36"/>
+      <c r="AD54" s="36"/>
+      <c r="AE54" s="36"/>
+      <c r="AF54" s="36"/>
+      <c r="AG54" s="36"/>
+      <c r="AH54" s="36"/>
+      <c r="AI54" s="36"/>
+      <c r="AJ54" s="36"/>
+      <c r="AK54" s="37"/>
     </row>
     <row r="55" spans="1:37" s="19" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="24"/>
-      <c r="B55" s="25"/>
-      <c r="C55" s="25"/>
-      <c r="D55" s="25"/>
-      <c r="E55" s="25"/>
-      <c r="F55" s="25"/>
-      <c r="G55" s="25"/>
-      <c r="H55" s="25"/>
-      <c r="I55" s="25"/>
-      <c r="J55" s="25"/>
-      <c r="K55" s="25"/>
-      <c r="L55" s="25"/>
-      <c r="M55" s="25"/>
-      <c r="N55" s="25"/>
-      <c r="O55" s="25"/>
-      <c r="P55" s="25"/>
-      <c r="Q55" s="25"/>
-      <c r="R55" s="25"/>
-      <c r="S55" s="25"/>
-      <c r="T55" s="25"/>
-      <c r="U55" s="25"/>
-      <c r="V55" s="25"/>
-      <c r="W55" s="25"/>
-      <c r="X55" s="25"/>
-      <c r="Y55" s="25"/>
-      <c r="Z55" s="25"/>
-      <c r="AA55" s="25"/>
-      <c r="AB55" s="25"/>
-      <c r="AC55" s="25"/>
-      <c r="AD55" s="25"/>
-      <c r="AE55" s="25"/>
-      <c r="AF55" s="25"/>
-      <c r="AG55" s="25"/>
-      <c r="AH55" s="25"/>
-      <c r="AI55" s="25"/>
-      <c r="AJ55" s="25"/>
-      <c r="AK55" s="26"/>
+      <c r="A55" s="35"/>
+      <c r="B55" s="36"/>
+      <c r="C55" s="36"/>
+      <c r="D55" s="36"/>
+      <c r="E55" s="36"/>
+      <c r="F55" s="36"/>
+      <c r="G55" s="36"/>
+      <c r="H55" s="36"/>
+      <c r="I55" s="36"/>
+      <c r="J55" s="36"/>
+      <c r="K55" s="36"/>
+      <c r="L55" s="36"/>
+      <c r="M55" s="36"/>
+      <c r="N55" s="36"/>
+      <c r="O55" s="36"/>
+      <c r="P55" s="36"/>
+      <c r="Q55" s="36"/>
+      <c r="R55" s="36"/>
+      <c r="S55" s="36"/>
+      <c r="T55" s="36"/>
+      <c r="U55" s="36"/>
+      <c r="V55" s="36"/>
+      <c r="W55" s="36"/>
+      <c r="X55" s="36"/>
+      <c r="Y55" s="36"/>
+      <c r="Z55" s="36"/>
+      <c r="AA55" s="36"/>
+      <c r="AB55" s="36"/>
+      <c r="AC55" s="36"/>
+      <c r="AD55" s="36"/>
+      <c r="AE55" s="36"/>
+      <c r="AF55" s="36"/>
+      <c r="AG55" s="36"/>
+      <c r="AH55" s="36"/>
+      <c r="AI55" s="36"/>
+      <c r="AJ55" s="36"/>
+      <c r="AK55" s="37"/>
     </row>
     <row r="56" spans="1:37" s="19" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="10"/>
@@ -3531,84 +3443,84 @@
       <c r="AK63" s="11"/>
     </row>
     <row r="64" spans="1:37" s="19" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="24" t="s">
-        <v>24</v>
+      <c r="A64" s="35" t="s">
+        <v>18</v>
       </c>
-      <c r="B64" s="25"/>
-      <c r="C64" s="25"/>
-      <c r="D64" s="25"/>
-      <c r="E64" s="25"/>
-      <c r="F64" s="25"/>
-      <c r="G64" s="25"/>
-      <c r="H64" s="25"/>
-      <c r="I64" s="25"/>
-      <c r="J64" s="25"/>
-      <c r="K64" s="25"/>
-      <c r="L64" s="25"/>
-      <c r="M64" s="25"/>
-      <c r="N64" s="25"/>
-      <c r="O64" s="25"/>
-      <c r="P64" s="25"/>
-      <c r="Q64" s="25"/>
-      <c r="R64" s="25"/>
-      <c r="S64" s="25"/>
-      <c r="T64" s="25"/>
-      <c r="U64" s="25"/>
-      <c r="V64" s="25"/>
-      <c r="W64" s="25"/>
-      <c r="X64" s="25"/>
-      <c r="Y64" s="25"/>
-      <c r="Z64" s="25"/>
-      <c r="AA64" s="25"/>
-      <c r="AB64" s="25"/>
-      <c r="AC64" s="25"/>
-      <c r="AD64" s="25"/>
-      <c r="AE64" s="25"/>
-      <c r="AF64" s="25"/>
-      <c r="AG64" s="25"/>
-      <c r="AH64" s="25"/>
-      <c r="AI64" s="25"/>
-      <c r="AJ64" s="25"/>
-      <c r="AK64" s="26"/>
+      <c r="B64" s="36"/>
+      <c r="C64" s="36"/>
+      <c r="D64" s="36"/>
+      <c r="E64" s="36"/>
+      <c r="F64" s="36"/>
+      <c r="G64" s="36"/>
+      <c r="H64" s="36"/>
+      <c r="I64" s="36"/>
+      <c r="J64" s="36"/>
+      <c r="K64" s="36"/>
+      <c r="L64" s="36"/>
+      <c r="M64" s="36"/>
+      <c r="N64" s="36"/>
+      <c r="O64" s="36"/>
+      <c r="P64" s="36"/>
+      <c r="Q64" s="36"/>
+      <c r="R64" s="36"/>
+      <c r="S64" s="36"/>
+      <c r="T64" s="36"/>
+      <c r="U64" s="36"/>
+      <c r="V64" s="36"/>
+      <c r="W64" s="36"/>
+      <c r="X64" s="36"/>
+      <c r="Y64" s="36"/>
+      <c r="Z64" s="36"/>
+      <c r="AA64" s="36"/>
+      <c r="AB64" s="36"/>
+      <c r="AC64" s="36"/>
+      <c r="AD64" s="36"/>
+      <c r="AE64" s="36"/>
+      <c r="AF64" s="36"/>
+      <c r="AG64" s="36"/>
+      <c r="AH64" s="36"/>
+      <c r="AI64" s="36"/>
+      <c r="AJ64" s="36"/>
+      <c r="AK64" s="37"/>
     </row>
     <row r="65" spans="1:37" s="19" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="24"/>
-      <c r="B65" s="25"/>
-      <c r="C65" s="25"/>
-      <c r="D65" s="25"/>
-      <c r="E65" s="25"/>
-      <c r="F65" s="25"/>
-      <c r="G65" s="25"/>
-      <c r="H65" s="25"/>
-      <c r="I65" s="25"/>
-      <c r="J65" s="25"/>
-      <c r="K65" s="25"/>
-      <c r="L65" s="25"/>
-      <c r="M65" s="25"/>
-      <c r="N65" s="25"/>
-      <c r="O65" s="25"/>
-      <c r="P65" s="25"/>
-      <c r="Q65" s="25"/>
-      <c r="R65" s="25"/>
-      <c r="S65" s="25"/>
-      <c r="T65" s="25"/>
-      <c r="U65" s="25"/>
-      <c r="V65" s="25"/>
-      <c r="W65" s="25"/>
-      <c r="X65" s="25"/>
-      <c r="Y65" s="25"/>
-      <c r="Z65" s="25"/>
-      <c r="AA65" s="25"/>
-      <c r="AB65" s="25"/>
-      <c r="AC65" s="25"/>
-      <c r="AD65" s="25"/>
-      <c r="AE65" s="25"/>
-      <c r="AF65" s="25"/>
-      <c r="AG65" s="25"/>
-      <c r="AH65" s="25"/>
-      <c r="AI65" s="25"/>
-      <c r="AJ65" s="25"/>
-      <c r="AK65" s="26"/>
+      <c r="A65" s="35"/>
+      <c r="B65" s="36"/>
+      <c r="C65" s="36"/>
+      <c r="D65" s="36"/>
+      <c r="E65" s="36"/>
+      <c r="F65" s="36"/>
+      <c r="G65" s="36"/>
+      <c r="H65" s="36"/>
+      <c r="I65" s="36"/>
+      <c r="J65" s="36"/>
+      <c r="K65" s="36"/>
+      <c r="L65" s="36"/>
+      <c r="M65" s="36"/>
+      <c r="N65" s="36"/>
+      <c r="O65" s="36"/>
+      <c r="P65" s="36"/>
+      <c r="Q65" s="36"/>
+      <c r="R65" s="36"/>
+      <c r="S65" s="36"/>
+      <c r="T65" s="36"/>
+      <c r="U65" s="36"/>
+      <c r="V65" s="36"/>
+      <c r="W65" s="36"/>
+      <c r="X65" s="36"/>
+      <c r="Y65" s="36"/>
+      <c r="Z65" s="36"/>
+      <c r="AA65" s="36"/>
+      <c r="AB65" s="36"/>
+      <c r="AC65" s="36"/>
+      <c r="AD65" s="36"/>
+      <c r="AE65" s="36"/>
+      <c r="AF65" s="36"/>
+      <c r="AG65" s="36"/>
+      <c r="AH65" s="36"/>
+      <c r="AI65" s="36"/>
+      <c r="AJ65" s="36"/>
+      <c r="AK65" s="37"/>
     </row>
     <row r="66" spans="1:37" s="19" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="10"/>
@@ -3963,12 +3875,18 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="A2:K3"/>
-    <mergeCell ref="L2:M3"/>
-    <mergeCell ref="AC2:AK3"/>
-    <mergeCell ref="A4:K5"/>
-    <mergeCell ref="L4:M5"/>
-    <mergeCell ref="Y4:AK5"/>
+    <mergeCell ref="A64:AK65"/>
+    <mergeCell ref="A25:H26"/>
+    <mergeCell ref="I25:X26"/>
+    <mergeCell ref="Y25:Z26"/>
+    <mergeCell ref="A28:H29"/>
+    <mergeCell ref="I28:AK29"/>
+    <mergeCell ref="A40:AK41"/>
+    <mergeCell ref="A22:H23"/>
+    <mergeCell ref="I22:AK23"/>
+    <mergeCell ref="A42:AK43"/>
+    <mergeCell ref="A44:AK45"/>
+    <mergeCell ref="A54:AK55"/>
     <mergeCell ref="AD6:AK7"/>
     <mergeCell ref="A9:AK10"/>
     <mergeCell ref="A12:AK16"/>
@@ -3983,18 +3901,12 @@
     <mergeCell ref="Y19:AA20"/>
     <mergeCell ref="AB19:AD20"/>
     <mergeCell ref="AE19:AI20"/>
-    <mergeCell ref="A22:H23"/>
-    <mergeCell ref="I22:AK23"/>
-    <mergeCell ref="A42:AK43"/>
-    <mergeCell ref="A44:AK45"/>
-    <mergeCell ref="A54:AK55"/>
-    <mergeCell ref="A64:AK65"/>
-    <mergeCell ref="A25:H26"/>
-    <mergeCell ref="I25:X26"/>
-    <mergeCell ref="Y25:Z26"/>
-    <mergeCell ref="A28:H29"/>
-    <mergeCell ref="I28:AK29"/>
-    <mergeCell ref="A40:AK41"/>
+    <mergeCell ref="A2:K3"/>
+    <mergeCell ref="L2:M3"/>
+    <mergeCell ref="AC2:AK3"/>
+    <mergeCell ref="A4:K5"/>
+    <mergeCell ref="L4:M5"/>
+    <mergeCell ref="Y4:AK5"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <dataValidations count="15">
